--- a/template/6.12/量化业务日报-2025-06-10.xlsx
+++ b/template/6.12/量化业务日报-2025-06-10.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,10 +31,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+    </font>
+    <font>
       <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +49,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D3"/>
         <bgColor rgb="00FCE4D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+        <bgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAEEF3"/>
+        <bgColor rgb="00DAEEF3"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,33 +134,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -249,6 +286,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -269,6 +331,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -309,6 +396,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -329,6 +441,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -369,6 +506,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -389,6 +551,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -691,10 +878,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
@@ -712,7 +899,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>（金额单位：元）</t>
+          <t>(金额单位：元)</t>
         </is>
       </c>
     </row>
@@ -793,66 +980,62 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>交易所回购</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>返息/逆回购</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>8888</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>98659.85000000001</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>总盈利/亏损（不含逆回购）</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-200718.67</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>-96323.48</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>收益率（不含逆回购）</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>-0.6691%</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>-0.3211%</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>总盈利/亏损（含逆回购）</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-96323.48</t>
-        </is>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>-209606.67</v>
       </c>
       <c r="C11" s="4" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>收益率（含逆回购）</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-0.3211%</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>-0.6987%</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -911,112 +1094,147 @@
       <c r="C17" s="4" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>昨日单位净值</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>0.99646</v>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>0.9930099999999999</v>
       </c>
       <c r="C18" s="4" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>单位净值(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
         <v>0.99679</v>
       </c>
       <c r="C19" s="4" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>日净值增长率</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>0.03304%</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>0.38058%</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>单位净值(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>0.9930099999999999</v>
+      </c>
+      <c r="C22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>-0.37891%</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>占用</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B25" s="7" t="n">
         <v>189165.6</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B26" s="7" t="n">
         <v>5888213.72</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>3.215%</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="140" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="140" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>今日交易: 2 只股指期货合约, 0 只股指期权合约， 成交合约价值 597.29 万元
 卖出开仓: IH2507(2 手),
@@ -1025,69 +1243,73 @@
 卖出平仓: IH2507(2 手)</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>买入股票: 0 只, 卖出股票: 1 只, 股票合计成交金额: 0.79 万元</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="140" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="140" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>当前持有: 2 只股指期货合约, 0 只股指期权合约, 持仓合约价值 315.48 万元, 其中: 
 多仓: IH2507(2 手),
 空仓: IH2507(2 手)</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">注:
 1、总盈利/亏损(不含逆回购): 根据032盈亏数据计算,未扣除中金所申报费。
-2、总盈利/亏损（含逆回购）：已扣除中金所申报费；按照O32盈亏数据计算的未扣除申报费的金额为：-102058.82 元。
+2、总盈利/亏损(含逆回购)：已扣除中金所申报费；按照O32盈亏数据计算的未扣除申报费的金额为：-110946.82 元。
+3、返息: 8888.0元。
 </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A25:C25"/>
+  <mergeCells count="23">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B4:C4"/>
@@ -1103,10 +1325,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1124,7 +1346,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>（金额单位：元）</t>
+          <t>(金额单位：元)</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1409,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5888213.67</v>
+        <v>5885719.94</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>24015462.8</v>
@@ -1200,95 +1422,93 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>29903676.47</v>
+        <v>29901182.74</v>
       </c>
       <c r="C7" s="4" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>交易所回购</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>返息/逆回购</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>8888</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>98659.85000000001</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>盈利/亏损（不含逆回购）</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>-111786.3300000001</v>
-      </c>
-      <c r="C9" s="7" t="n">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>盈利/亏损(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>-114280.06</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>15462.8</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>-98817.25999999791</v>
+      </c>
+      <c r="C10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>-0.3294%</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>盈利/亏损(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>-123168.0599999996</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>-83197.14</v>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>总盈利/亏损（不含逆回购）</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>-194983.4700000001</v>
-      </c>
-      <c r="C10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>收益率（不含逆回购）</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-0.6499%</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>盈利/亏损（含逆回购）</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>-111786.33</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>15462.8</v>
-      </c>
-    </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>总盈利/亏损（含逆回购）</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>-96323.53000000119</v>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>-197477.1999999996</v>
       </c>
       <c r="C13" s="4" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>收益率（含逆回购）</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-0.3211%</t>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>-0.6583%</t>
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -1320,7 +1540,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>29903676.47</v>
+        <v>29901182.74</v>
       </c>
       <c r="C17" s="4" t="n"/>
     </row>
@@ -1347,112 +1567,147 @@
       <c r="C19" s="4" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>昨日单位净值</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>0.99652</v>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>0.99342</v>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>单位净值(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>0.99671</v>
+      </c>
+      <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>0.33079%</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>日净值增长率</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>0.02702%</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>单位净值(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>0.99342</v>
+      </c>
+      <c r="C24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含逆回购/返息)</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>-0.33834%</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>占用</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B27" s="16" t="n">
         <v>189165.6</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>5888213.67</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="B28" s="7" t="n">
+        <v>5885719.94</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>3.2126%</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>3.214%</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="140" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="140" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>今日交易: 2 只股指期货合约, 0 只股指期权合约， 成交合约价值 597.29 万元
 卖出开仓: IH2507(2 手),
@@ -1461,68 +1716,72 @@
 卖出平仓: IH2507(2 手)</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>买入股票: 0 只, 卖出股票: 1 只, 股票合计成交金额: 0.79 万元</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="140" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="140" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>当前持有: 2 只股指期货合约, 0 只股指期权合约, 持仓合约价值 315.48 万元, 其中: 
 多仓: IH2507(2 手),
 空仓: IH2507(2 手)</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>注:
-1、盈利/亏损（不含逆回购）数据暂未包含中金所申报费，盈利/亏损（含逆回购）数据已包含中金所申报费。</t>
+1、盈利/亏损(不含逆回购)数据暂未包含中金所申报费，盈利/亏损(含逆回购)数据已包含中金所申报费。
+2、返息: 8888.0元。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="23">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A27:C27"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A29:C29"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A31:C31"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
@@ -1537,10 +1796,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1550,9 +1809,9 @@
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>2025-06-10, （金额单位：元）</t>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>2025-06-10, (金额单位：元)</t>
         </is>
       </c>
     </row>
@@ -1611,160 +1870,224 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>总盈利/亏损</t>
+          <t>返息</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
+        <v>6666</v>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>-69232.84</v>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>收益率</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>-0.6923%</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>-75898.84</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>-0.759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>资产净值</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>9930767.16</v>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>总份额</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>10000000</v>
-      </c>
+      <c r="B12" s="4" t="n"/>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>期初单位净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>昨日单位净值</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>0.9930600000000001</v>
+          <t>资产净值</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>9930767.16</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>0.99308</v>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>10000000</v>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>日净值增长率</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>0.00168%</t>
-        </is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含返息)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>0.99241</v>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>单位净值(含返息)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>0.99308</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>0.06718%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含返息)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>0.99308</v>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>0.99241</v>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>-0.06746%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>占用</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B24" s="7" t="n">
         <v>1171175.35</v>
       </c>
     </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B25" s="7" t="n">
         <v>9930767.16</v>
       </c>
     </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>11.7825%</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="140" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="140" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>今日交易 23 只期货合约 成交合约价值 284.54 万元
 卖出开仓: 8 只
@@ -1773,54 +2096,60 @@
 卖出平仓: 7 只</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="140" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="140" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>共持仓 39只期货， 持仓合约价值 1240.73 万元, 其中空仓: 18 只,多仓: 21 只</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C30" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B30"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
+    <mergeCell ref="B26"/>
     <mergeCell ref="B7"/>
+    <mergeCell ref="B25"/>
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B22"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B12"/>
     <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="B14"/>
     <mergeCell ref="B1"/>
     <mergeCell ref="B8"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="B13"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B28"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1834,10 +2163,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1849,7 +2178,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2025-06-10, （金额单位：元）</t>
+          <t>2025-06-10, (金额单位：元)</t>
         </is>
       </c>
     </row>
@@ -1902,166 +2231,230 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>9924444</v>
+        <v>10031521</v>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>总盈利/亏损</t>
+          <t>返息</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-75556</v>
+        <v>6666</v>
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>收益率</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-0.7556%</t>
-        </is>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>31521</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>0.3152%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>24855</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>0.2485%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>资产净值</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>9924444</v>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>总份额</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>10000000</v>
-      </c>
+      <c r="B12" s="4" t="n"/>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>期初单位净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>昨日单位净值</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>0.9946</v>
+          <t>资产净值</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>10031521</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>0.99244</v>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>10000000</v>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>日净值增长率</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>-0.21673%</t>
-        </is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含返息)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1.00645</v>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>单位净值(含返息)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1.00315</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>-0.32768%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含返息)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>1.00645</v>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>1.00249</v>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>-0.39391%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>占用</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B24" s="7" t="n">
         <v>1171175.35</v>
       </c>
     </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>9924444</v>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B25" s="7" t="n">
+        <v>10031521</v>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>11.8009%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>11.675%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="140" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="140" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>今日交易 23 只期货合约 成交合约价值 284.54 万元
 卖出开仓: 8 只
@@ -2070,54 +2463,60 @@
 卖出平仓: 7 只</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="140" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="140" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>共持仓 39只期货， 持仓合约价值 1240.73 万元, 其中空仓: 18 只,多仓: 21 只</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C30" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B30"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
+    <mergeCell ref="B26"/>
     <mergeCell ref="B7"/>
+    <mergeCell ref="B25"/>
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B22"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B12"/>
     <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="B14"/>
     <mergeCell ref="B1"/>
     <mergeCell ref="B8"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="B13"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B28"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2131,10 +2530,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2144,9 +2543,9 @@
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>2025-06-10, （金额单位：元）</t>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>2025-06-10, (金额单位：元)</t>
         </is>
       </c>
     </row>
@@ -2205,224 +2604,292 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>总盈利/亏损</t>
+          <t>返息</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>240.15</v>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>收益率</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>0.0048%</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>-9758.85</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>-0.1952%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>资产净值</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>5000240.15</v>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>总份额</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>5000000</v>
-      </c>
+      <c r="B12" s="4" t="n"/>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>期初单位净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>昨日单位净值</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>0.99988</v>
+          <t>资产净值</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>5000240.15</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1.00005</v>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>5000000</v>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>日净值增长率</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>0.01681%</t>
-        </is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含返息)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1.00623</v>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>单位净值(含返息)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1.00005</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>-0.61437%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含返息)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>1.00623</v>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>0.99805</v>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>-0.81311%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>占用</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B24" s="7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B25" s="7" t="n">
         <v>5000240.15</v>
       </c>
     </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="140" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="140" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">今日交易 2 只期货, 成交合约价值 2989.31 万元,其中
-1,国债期货:
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>今日交易 2 只期货, 成交合约价值 2989.31 万元,其中
+1.国债期货:
 买入开仓: 2只 (T2509,TL2509)
 卖出平仓: 2只 (T2509,TL2509)
-2,黄金期货:无
-3,铜期货:无
-4,其他品种:无
-</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+2.黄金期货:无
+3.铜期货:无
+4.其他品种:无</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="140" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="140" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">共持仓: 0 只期货, 持仓合约价值 0.0 万元, 其中: 
 国债期货 0只 
 黄金期货 0只 
 铜期货 0只 
-其他品种 0只 
-</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n"/>
+其他品种 0只 </t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B30"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
+    <mergeCell ref="B26"/>
     <mergeCell ref="B7"/>
+    <mergeCell ref="B25"/>
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B22"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B12"/>
     <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="B14"/>
     <mergeCell ref="B1"/>
     <mergeCell ref="B8"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="B13"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B28"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2436,10 +2903,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2451,7 +2918,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2025-06-10, （金额单位：元）</t>
+          <t>2025-06-10, (金额单位：元)</t>
         </is>
       </c>
     </row>
@@ -2504,230 +2971,298 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5000240.05</v>
+        <v>5000333</v>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>总盈利/亏损</t>
+          <t>返息</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>240.0499999998137</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>收益率</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>0.0048%</t>
-        </is>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>333</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>0.0067%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>-9666</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>-0.1933%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>资产净值</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>5000240.05</v>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>总份额</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>5000000</v>
-      </c>
+      <c r="B12" s="4" t="n"/>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>期初单位净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>昨日单位净值</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>0.99988</v>
+          <t>资产净值</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>5000333</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1.00005</v>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>5000000</v>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>日净值增长率</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>0.0168%</t>
-        </is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含返息)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1.00645</v>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>单位净值(含返息)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1.00007</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>-0.63425%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含返息)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>1.00645</v>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>0.99807</v>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>-0.83295%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>占用</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B24" s="7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>5000240.05</v>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B25" s="7" t="n">
+        <v>5000333</v>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="140" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="140" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">今日交易 2 只期货, 成交合约价值 2989.31 万元,其中
-1,国债期货:
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>今日交易 2 只期货, 成交合约价值 2989.31 万元,其中
+1.国债期货:
 买入开仓: 2只 (T2509,TL2509)
 卖出平仓: 2只 (T2509,TL2509)
-2,黄金期货:无
-3,铜期货:无
-4,其他品种:无
-</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+2.黄金期货:无
+3.铜期货:无
+4.其他品种:无</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="140" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="140" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">共持仓: 0 只期货, 持仓合约价值 0.0 万元, 其中: 
 国债期货 0只 
 黄金期货 0只 
 铜期货 0只 
-其他品种 0只 
-</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n"/>
+其他品种 0只 </t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B30"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
+    <mergeCell ref="B26"/>
     <mergeCell ref="B7"/>
+    <mergeCell ref="B25"/>
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B22"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B12"/>
     <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="B14"/>
     <mergeCell ref="B1"/>
     <mergeCell ref="B8"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="B13"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B28"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/template/6.12/量化业务日报-2025-06-10.xlsx
+++ b/template/6.12/量化业务日报-2025-06-10.xlsx
@@ -878,10 +878,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
@@ -980,7 +980,7 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>返息/逆回购</t>
+          <t>返息、逆回购</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -991,210 +991,210 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>-96323.48</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>555</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>收益率(含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
+          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>-96323.48</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>-0.3211%</t>
         </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(不含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>-203871.3300000005</v>
       </c>
       <c r="C11" s="4" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>收益率(不含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>-0.6796%</t>
-        </is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>-204426.3300000005</v>
       </c>
       <c r="C12" s="4" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>-0.6814%</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>30000000</v>
-      </c>
+      <c r="B14" s="3" t="n"/>
       <c r="C14" s="4" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>资产净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>29903676.52</v>
+        <v>30000000</v>
       </c>
       <c r="C15" s="4" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>总份额</t>
+          <t>资产净值</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>30000000</v>
+        <v>29903676.52</v>
       </c>
       <c r="C16" s="4" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>期初单位净值</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B18" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="C17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>昨日单位净值(含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>0.9932</v>
       </c>
       <c r="C18" s="4" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>单位净值(含逆回购/返息)</t>
+          <t>昨日单位净值(含返息、逆回购、手续费)</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.99679</v>
+        <v>0.99319</v>
       </c>
       <c r="C19" s="4" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>日净值增长率(含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>0.36138%</t>
-        </is>
+          <t>单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>0.99679</v>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>昨日单位净值(不含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>0.99679</v>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>0.36239%</t>
+        </is>
       </c>
       <c r="C21" s="4" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>单位净值(不含逆回购/返息)</t>
+          <t>昨日单位净值(不含返息、逆回购、手续费)</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.9932</v>
+        <v>0.99679</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>日净值增长率(不含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>-0.35973%</t>
-        </is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>0.99319</v>
       </c>
       <c r="C23" s="4" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>-0.36158%</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="4" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>189165.6</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="4" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>账户权益</t>
+          <t>占用</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>5888213.72</v>
+        <v>189165.6</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1205,36 +1205,51 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>5888213.72</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>3.215%</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="140" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="140" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>今日交易: 2 只股指期货合约, 0 只股指期权合约， 成交合约价值 597.29 万元
 卖出开仓: IH2507(2 手),
@@ -1243,46 +1258,46 @@
 卖出平仓: IH2507(2 手)</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>买入股票: 0 只, 卖出股票: 1 只, 股票合计成交金额: 0.79 万元</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="140" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="140" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>当前持有: 2 只股指期货合约, 0 只股指期权合约, 持仓合约价值 315.48 万元, 其中: 
 多仓: IH2507(2 手),
 空仓: IH2507(2 手)</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="80" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">注:
 1、总盈利/亏损(不含逆回购): 根据032盈亏数据计算,未扣除中金所申报费。
-2、总盈利/亏损(含逆回购)：已扣除中金所申报费；按照O32盈亏数据计算的未扣除申报费的金额为：-105211.48 元。
+2、总盈利/亏损(含逆回购)：已扣除中金所申报费；按照O32盈亏数据计算的未扣除申报费的金额为：-105766.48 元。
 3、返息: 8888.0元。
 </t>
         </is>
@@ -1290,6 +1305,7 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
@@ -1298,18 +1314,17 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B4:C4"/>
@@ -1325,10 +1340,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1429,7 +1444,7 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>返息/逆回购</t>
+          <t>返息、逆回购</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -1440,234 +1455,234 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>盈利/亏损(含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>-114280.06</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>15462.8</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>555</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>总盈利/亏损(含逆回购/返息)</t>
+          <t>盈利/亏损(含返息、逆回购、手续费)</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>-98817.25999999791</v>
-      </c>
-      <c r="C10" s="4" t="n"/>
+        <v>-114280.06</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>15462.8</v>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>收益率(含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>-98817.25999999791</v>
+      </c>
+      <c r="C11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>-0.3294%</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>盈利/亏损(不含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>-123168.0599999996</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>-83197.14</v>
-      </c>
+      <c r="C12" s="4" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>总盈利/亏损(不含逆回购/返息)</t>
+          <t>盈利/亏损(不含返息、逆回购、手续费)</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>-206365.1099999979</v>
-      </c>
-      <c r="C13" s="4" t="n"/>
+        <v>-123168.0599999996</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>-83197.14</v>
+      </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>收益率(不含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>-0.6879%</t>
-        </is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>-206920.1099999979</v>
       </c>
       <c r="C14" s="4" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>-0.6897%</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>30000000</v>
-      </c>
+      <c r="B16" s="3" t="n"/>
       <c r="C16" s="4" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>资产净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>29901182.74</v>
+        <v>30000000</v>
       </c>
       <c r="C17" s="4" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>总份额</t>
+          <t>资产净值</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>30000000</v>
+        <v>29901182.74</v>
       </c>
       <c r="C18" s="4" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>期初单位净值</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B20" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="C19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>昨日单位净值(含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>0.99312</v>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>单位净值(含逆回购/返息)</t>
+          <t>昨日单位净值(含返息、逆回购、手续费)</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.99671</v>
+        <v>0.9931</v>
       </c>
       <c r="C21" s="4" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>日净值增长率(含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>0.36109%</t>
-        </is>
+          <t>单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>0.99671</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>昨日单位净值(不含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>0.99679</v>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>0.36311%</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>单位净值(不含逆回购/返息)</t>
+          <t>昨日单位净值(不含返息、逆回购、手续费)</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>0.99312</v>
+        <v>0.99679</v>
       </c>
       <c r="C24" s="4" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>日净值增长率(不含逆回购/返息)</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>-0.36807%</t>
-        </is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0.9931</v>
       </c>
       <c r="C25" s="4" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>-0.36992%</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>189165.6</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="4" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>账户权益</t>
+          <t>占用</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>5885719.94</v>
+        <v>189165.6</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1678,36 +1693,51 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>5885719.94</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>3.214%</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="140" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="140" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>今日交易: 2 只股指期货合约, 0 只股指期权合约， 成交合约价值 597.29 万元
 卖出开仓: IH2507(2 手),
@@ -1716,42 +1746,42 @@
 卖出平仓: IH2507(2 手)</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>买入股票: 0 只, 卖出股票: 1 只, 股票合计成交金额: 0.79 万元</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="140" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="140" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>当前持有: 2 只股指期货合约, 0 只股指期权合约, 持仓合约价值 315.48 万元, 其中: 
 多仓: IH2507(2 手),
 空仓: IH2507(2 手)</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="80" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>注:
 1、盈利/亏损(不含逆回购)数据暂未包含中金所申报费，盈利/亏损(含逆回购)数据已包含中金所申报费。
@@ -1761,29 +1791,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A32:C32"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1796,10 +1826,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1878,216 +1908,226 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(含返息)</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>-69232.84</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>444</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>收益率(含返息)</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>-0.6923%</t>
-        </is>
+          <t>总盈利/亏损(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>-69232.84</v>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>总盈利/亏损(不含返息)</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>-75898.84</v>
+          <t>收益率(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>-0.6923%</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>收益率(不含返息)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>-0.759%</t>
-        </is>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>-76342.84</v>
       </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>-0.7634%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>10000000</v>
-      </c>
+      <c r="B13" s="4" t="n"/>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>资产净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>9930767.16</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>总份额</t>
+          <t>资产净值</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>10000000</v>
+        <v>9930767.16</v>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>期初单位净值</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B17" s="7" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>昨日单位净值(含返息)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>0.99241</v>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>单位净值(含返息)</t>
+          <t>昨日单位净值(含返息、手续费)</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>0.99308</v>
+        <v>0.99237</v>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>日净值增长率(含返息)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>0.06718%</t>
-        </is>
+          <t>单位净值(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>0.99308</v>
       </c>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>昨日单位净值(不含返息)</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>0.99308</v>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>0.07121%</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>单位净值(不含返息)</t>
+          <t>昨日单位净值(不含返息、手续费)</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.99241</v>
+        <v>0.99308</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>日净值增长率(不含返息)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>-0.06746%</t>
-        </is>
+          <t>单位净值(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>0.99237</v>
       </c>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>-0.07193%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>1171175.35</v>
-      </c>
+      <c r="B24" s="4" t="n"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>账户权益</t>
+          <t>占用</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>9930767.16</v>
+        <v>1171175.35</v>
       </c>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>9930767.16</v>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>11.7825%</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="140" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="140" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>今日交易 23 只期货合约 成交合约价值 284.54 万元
 卖出开仓: 8 只
@@ -2096,36 +2136,36 @@
 卖出平仓: 7 只</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n"/>
-    </row>
-    <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="140" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="140" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>共持仓 39只期货， 持仓合约价值 1240.73 万元, 其中空仓: 18 只,多仓: 21 只</t>
         </is>
       </c>
-      <c r="C30" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B9"/>
-    <mergeCell ref="B30"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
-    <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
@@ -2135,21 +2175,22 @@
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="B31"/>
+    <mergeCell ref="B27"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B12"/>
     <mergeCell ref="B18"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A23:B23"/>
     <mergeCell ref="B14"/>
+    <mergeCell ref="B23"/>
     <mergeCell ref="B1"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="B17"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B13"/>
+    <mergeCell ref="B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="B28"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2163,10 +2204,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2245,216 +2286,226 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(含返息)</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>31521</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>444</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>收益率(含返息)</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
+          <t>总盈利/亏损(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>31521</v>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>0.3152%</t>
         </is>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(不含返息)</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>24855</v>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>收益率(不含返息)</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>0.2485%</t>
-        </is>
+          <t>总盈利/亏损(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>24411</v>
       </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>0.2441%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>10000000</v>
-      </c>
+      <c r="B13" s="4" t="n"/>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>资产净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>10031521</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>总份额</t>
+          <t>资产净值</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>10000000</v>
+        <v>10031521</v>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>期初单位净值</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B17" s="7" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>昨日单位净值(含返息)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>1.00645</v>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>单位净值(含返息)</t>
+          <t>昨日单位净值(含返息、手续费)</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>1.00315</v>
+        <v>1.00645</v>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>日净值增长率(含返息)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
+          <t>单位净值(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1.00315</v>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>-0.32768%</t>
         </is>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>昨日单位净值(不含返息)</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>1.00645</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>单位净值(不含返息)</t>
+          <t>昨日单位净值(不含返息、手续费)</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1.00249</v>
+        <v>1.00645</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>日净值增长率(不含返息)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>-0.39391%</t>
-        </is>
+          <t>单位净值(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>1.00244</v>
       </c>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>-0.39832%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>1171175.35</v>
-      </c>
+      <c r="B24" s="4" t="n"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>账户权益</t>
+          <t>占用</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>10031521</v>
+        <v>1171175.35</v>
       </c>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>10031521</v>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>11.675%</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="140" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="140" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>今日交易 23 只期货合约 成交合约价值 284.54 万元
 卖出开仓: 8 只
@@ -2463,36 +2514,36 @@
 卖出平仓: 7 只</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n"/>
-    </row>
-    <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="140" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="140" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>共持仓 39只期货， 持仓合约价值 1240.73 万元, 其中空仓: 18 只,多仓: 21 只</t>
         </is>
       </c>
-      <c r="C30" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B9"/>
-    <mergeCell ref="B30"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
-    <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
@@ -2502,21 +2553,22 @@
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="B31"/>
+    <mergeCell ref="B27"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B12"/>
     <mergeCell ref="B18"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A23:B23"/>
     <mergeCell ref="B14"/>
+    <mergeCell ref="B23"/>
     <mergeCell ref="B1"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="B17"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B13"/>
+    <mergeCell ref="B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="B28"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2530,10 +2582,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2612,216 +2664,226 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(含返息)</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>240.15</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>333</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>收益率(含返息)</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+          <t>总盈利/亏损(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>240.15</v>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>0.0048%</t>
         </is>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(不含返息)</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>-9758.85</v>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>收益率(不含返息)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>-0.1952%</t>
-        </is>
+          <t>总盈利/亏损(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>-10091.85</v>
       </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>-0.2018%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>5000000</v>
-      </c>
+      <c r="B13" s="4" t="n"/>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>资产净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>5000240.15</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>总份额</t>
+          <t>资产净值</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5000000</v>
+        <v>5000240.15</v>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>期初单位净值</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B17" s="7" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>昨日单位净值(含返息)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>1.00623</v>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>单位净值(含返息)</t>
+          <t>昨日单位净值(含返息、手续费)</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>1.00005</v>
+        <v>1.00623</v>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>日净值增长率(含返息)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
+          <t>单位净值(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1.00005</v>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>-0.61437%</t>
         </is>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>昨日单位净值(不含返息)</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>1.00623</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>单位净值(不含返息)</t>
+          <t>昨日单位净值(不含返息、手续费)</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.99805</v>
+        <v>1.00623</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>日净值增长率(不含返息)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>-0.81311%</t>
-        </is>
+          <t>单位净值(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>0.99798</v>
       </c>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>-0.81973%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" s="4" t="n"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>账户权益</t>
+          <t>占用</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>5000240.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>5000240.15</v>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="140" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="140" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>今日交易 2 只期货, 成交合约价值 2989.31 万元,其中
 1.国债期货:
@@ -2832,23 +2894,23 @@
 4.其他品种:无</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n"/>
-    </row>
-    <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="140" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="140" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">共持仓: 0 只期货, 持仓合约价值 0.0 万元, 其中: 
 国债期货 0只 
@@ -2857,15 +2919,15 @@
 其他品种 0只 </t>
         </is>
       </c>
-      <c r="C30" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B9"/>
-    <mergeCell ref="B30"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
-    <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
@@ -2875,21 +2937,22 @@
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="B31"/>
+    <mergeCell ref="B27"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B12"/>
     <mergeCell ref="B18"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A23:B23"/>
     <mergeCell ref="B14"/>
+    <mergeCell ref="B23"/>
     <mergeCell ref="B1"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="B17"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B13"/>
+    <mergeCell ref="B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="B28"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2903,10 +2966,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2985,216 +3048,226 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(含返息)</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
         <v>333</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>收益率(含返息)</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+          <t>总盈利/亏损(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>收益率(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>0.0067%</t>
         </is>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(不含返息)</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>-9666</v>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>收益率(不含返息)</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>-0.1933%</t>
-        </is>
+          <t>总盈利/亏损(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>5000000</v>
-      </c>
+      <c r="B13" s="4" t="n"/>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>资产净值</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>5000333</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>总份额</t>
+          <t>资产净值</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5000000</v>
+        <v>5000333</v>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>期初单位净值</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B17" s="7" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>昨日单位净值(含返息)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>1.00645</v>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>单位净值(含返息)</t>
+          <t>昨日单位净值(含返息、手续费)</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>1.00007</v>
+        <v>1.00645</v>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>日净值增长率(含返息)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
+          <t>单位净值(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1.00007</v>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>-0.63425%</t>
         </is>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>昨日单位净值(不含返息)</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>1.00645</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>单位净值(不含返息)</t>
+          <t>昨日单位净值(不含返息、手续费)</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.99807</v>
+        <v>1.00645</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>日净值增长率(不含返息)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>-0.83295%</t>
-        </is>
+          <t>单位净值(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、手续费)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>-0.83956%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" s="4" t="n"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>账户权益</t>
+          <t>占用</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>5000333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>5000333</v>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="140" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="140" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>今日交易 2 只期货, 成交合约价值 2989.31 万元,其中
 1.国债期货:
@@ -3205,23 +3278,23 @@
 4.其他品种:无</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n"/>
-    </row>
-    <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="140" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="140" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">共持仓: 0 只期货, 持仓合约价值 0.0 万元, 其中: 
 国债期货 0只 
@@ -3230,15 +3303,15 @@
 其他品种 0只 </t>
         </is>
       </c>
-      <c r="C30" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B9"/>
-    <mergeCell ref="B30"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
-    <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
@@ -3248,21 +3321,22 @@
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="B31"/>
+    <mergeCell ref="B27"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B12"/>
     <mergeCell ref="B18"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A23:B23"/>
     <mergeCell ref="B14"/>
+    <mergeCell ref="B23"/>
     <mergeCell ref="B1"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="B17"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B13"/>
+    <mergeCell ref="B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="B28"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/template/6.12/量化业务日报-2025-06-10.xlsx
+++ b/template/6.12/量化业务日报-2025-06-10.xlsx
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>-209606.67</v>
+        <v>-203871.3300000005</v>
       </c>
       <c r="C11" s="4" t="n"/>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>-0.6987%</t>
+          <t>-0.6796%</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>0.9930099999999999</v>
+        <v>0.9932</v>
       </c>
       <c r="C18" s="4" t="n"/>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>0.38058%</t>
+          <t>0.36138%</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.9930099999999999</v>
+        <v>0.9932</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>-0.37891%</t>
+          <t>-0.35973%</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1282,7 +1282,7 @@
         <is>
           <t xml:space="preserve">注:
 1、总盈利/亏损(不含逆回购): 根据032盈亏数据计算,未扣除中金所申报费。
-2、总盈利/亏损(含逆回购)：已扣除中金所申报费；按照O32盈亏数据计算的未扣除申报费的金额为：-110946.82 元。
+2、总盈利/亏损(含逆回购)：已扣除中金所申报费；按照O32盈亏数据计算的未扣除申报费的金额为：-105211.48 元。
 3、返息: 8888.0元。
 </t>
         </is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>-197477.1999999996</v>
+        <v>-206365.1099999979</v>
       </c>
       <c r="C13" s="4" t="n"/>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>-0.6583%</t>
+          <t>-0.6879%</t>
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0.99342</v>
+        <v>0.99312</v>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>0.33079%</t>
+          <t>0.36109%</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>0.99342</v>
+        <v>0.99312</v>
       </c>
       <c r="C24" s="4" t="n"/>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>-0.33834%</t>
+          <t>-0.36807%</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -1651,7 +1651,7 @@
           <t>占用</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="7" t="n">
         <v>189165.6</v>
       </c>
       <c r="C27" s="6" t="inlineStr">

--- a/template/6.12/量化业务日报-2025-06-10.xlsx
+++ b/template/6.12/量化业务日报-2025-06-10.xlsx
@@ -13,6 +13,7 @@
     <sheet name="量化二-收盘数据" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="量化三-结算数据" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="量化三-收盘数据" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="量化二持仓信息" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +39,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +62,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="00DAEEF3"/>
         <bgColor rgb="00DAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADADE"/>
+        <bgColor rgb="00FADADE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2D9"/>
+        <bgColor rgb="00E3F2D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4D1"/>
+        <bgColor rgb="00FFF4D1"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -182,6 +201,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2154,7 +2188,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>共持仓 39只期货， 持仓合约价值 1240.73 万元, 其中空仓: 18 只,多仓: 21 只</t>
+          <t>共持仓 41只期货， 持仓合约价值 2740.73 万元, 其中空仓: 19 只,多仓: 22 只</t>
         </is>
       </c>
       <c r="C31" s="17" t="n"/>
@@ -2532,7 +2566,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>共持仓 39只期货， 持仓合约价值 1240.73 万元, 其中空仓: 18 只,多仓: 21 只</t>
+          <t>共持仓 41只期货， 持仓合约价值 2740.73 万元, 其中空仓: 19 只,多仓: 22 只</t>
         </is>
       </c>
       <c r="C31" s="17" t="n"/>
@@ -3342,4 +3376,283 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>量化二持仓信息</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>统计日期</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>单位：万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>多头市值</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>空头市值</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>净市值</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>农副</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n">
+        <v>233.33</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>105.38</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>127.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>333.66</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>245.54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="20" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>192.07</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>-152.89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>49.22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>贵金属</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>13.39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>股指期货</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>1352.77</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>657.74</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>695.03</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>2035.25</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>1020.96</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>1014.29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>汇总</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>风险度：</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>11.7825</v>
+      </c>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>权益：</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>9930767.16</v>
+      </c>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>当日盈亏：</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>8888</v>
+      </c>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>总市值：</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>2740.73</v>
+      </c>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>去锁市值：</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>18407335</v>
+      </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>平仓盈亏：</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>